--- a/data/reviews-clients.xlsx
+++ b/data/reviews-clients.xlsx
@@ -1,41 +1,152 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://eurecatcloud-my.sharepoint.com/personal/alana_olivieri_eurecat_org/Documents/Formaciones/DonaIndustria4.0/Dia_3/Recursos/n8n-automation/data/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="3" documentId="11_4E17431850397D6A206102AB8855B237A12CC87D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{637644BD-1393-43F0-8829-7C5EEAA365CA}"/>
+  <bookViews>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="40">
+  <si>
+    <t>Nombre</t>
+  </si>
+  <si>
+    <t>Apellido</t>
+  </si>
+  <si>
+    <t>Review</t>
+  </si>
+  <si>
+    <t>Fecha</t>
+  </si>
+  <si>
+    <t>Valoración</t>
+  </si>
+  <si>
+    <t>Email_ID</t>
+  </si>
+  <si>
+    <t>Laura</t>
+  </si>
+  <si>
+    <t>Martínez</t>
+  </si>
+  <si>
+    <t>La máquina se detuvo dos veces durante el turno.</t>
+  </si>
+  <si>
+    <t>2.0</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Carlos</t>
+  </si>
+  <si>
+    <t>Ruiz</t>
+  </si>
+  <si>
+    <t>El proceso fue estable y sin incidencias.</t>
+  </si>
+  <si>
+    <t>5.5</t>
+  </si>
+  <si>
+    <t>Marta</t>
+  </si>
+  <si>
+    <t>Gómez</t>
+  </si>
+  <si>
+    <t>La interfaz es clara, pero el informe tarda en cargar.</t>
+  </si>
+  <si>
+    <t>3.6</t>
+  </si>
+  <si>
+    <t>Diego</t>
+  </si>
+  <si>
+    <t>Santos</t>
+  </si>
+  <si>
+    <t>Se perdieron datos al importar el archivo.</t>
+  </si>
+  <si>
+    <t>1.7</t>
+  </si>
+  <si>
+    <t>Nuria</t>
+  </si>
+  <si>
+    <t>Pérez</t>
+  </si>
+  <si>
+    <t>Buen funcionamiento general.</t>
+  </si>
+  <si>
+    <t>4.5</t>
+  </si>
+  <si>
+    <t>Javier</t>
+  </si>
+  <si>
+    <t>López</t>
+  </si>
+  <si>
+    <t>El sistema respondió correctamente durante toda la prueba.</t>
+  </si>
+  <si>
+    <t>Sonia</t>
+  </si>
+  <si>
+    <t>Navarro</t>
+  </si>
+  <si>
+    <t>Necesitamos más filtros para encontrar la información.</t>
+  </si>
+  <si>
+    <t>Álex</t>
+  </si>
+  <si>
+    <t>Romero</t>
+  </si>
+  <si>
+    <t>El cálculo mostrado no coincide con el esperado.</t>
+  </si>
+  <si>
+    <t>Ana prueba</t>
+  </si>
+  <si>
+    <t>El pedido llegó tarde, con el envase roto y nadie avisó</t>
+  </si>
+  <si>
+    <t>2026-10-23T15:45:52.000Z</t>
+  </si>
+  <si>
+    <t>1a16970c12b383d6</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -65,13 +176,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -396,242 +515,214 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:F10"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Nombre</v>
-      </c>
-      <c r="B1" t="str">
-        <v>Apellido</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Review</v>
-      </c>
-      <c r="D1" t="str">
-        <v>estrellitas</v>
-      </c>
-      <c r="E1" t="str">
-        <v>Fecha</v>
-      </c>
-      <c r="F1" t="str">
-        <v>Valoración</v>
-      </c>
-      <c r="G1" t="str">
-        <v>Email_ID</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>Laura</v>
-      </c>
-      <c r="B2" t="str">
-        <v>Martínez</v>
-      </c>
-      <c r="C2" t="str">
-        <v>La máquina se detuvo dos veces durante el turno.</v>
-      </c>
-      <c r="D2" t="str">
-        <v>2.0</v>
-      </c>
-      <c r="E2" t="str">
-        <v/>
-      </c>
-      <c r="F2" t="str">
-        <v/>
-      </c>
-      <c r="G2" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>Carlos</v>
-      </c>
-      <c r="B3" t="str">
-        <v>Ruiz</v>
-      </c>
-      <c r="C3" t="str">
-        <v>El proceso fue estable y sin incidencias.</v>
-      </c>
-      <c r="D3" t="str">
-        <v>5.5</v>
-      </c>
-      <c r="E3" t="str">
-        <v/>
-      </c>
-      <c r="F3" t="str">
-        <v/>
-      </c>
-      <c r="G3" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>Marta</v>
-      </c>
-      <c r="B4" t="str">
-        <v>Gómez</v>
-      </c>
-      <c r="C4" t="str">
-        <v>La interfaz es clara, pero el informe tarda en cargar.</v>
-      </c>
-      <c r="D4" t="str">
-        <v>3.6</v>
-      </c>
-      <c r="E4" t="str">
-        <v/>
-      </c>
-      <c r="F4" t="str">
-        <v/>
-      </c>
-      <c r="G4" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>Diego</v>
-      </c>
-      <c r="B5" t="str">
-        <v>Santos</v>
-      </c>
-      <c r="C5" t="str">
-        <v>Se perdieron datos al importar el archivo.</v>
-      </c>
-      <c r="D5" t="str">
-        <v>1.7</v>
-      </c>
-      <c r="E5" t="str">
-        <v/>
-      </c>
-      <c r="F5" t="str">
-        <v/>
-      </c>
-      <c r="G5" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>Nuria</v>
-      </c>
-      <c r="B6" t="str">
-        <v>Pérez</v>
-      </c>
-      <c r="C6" t="str">
-        <v>Buen funcionamiento general.</v>
-      </c>
-      <c r="D6" t="str">
-        <v>4.5</v>
-      </c>
-      <c r="E6" t="str">
-        <v/>
-      </c>
-      <c r="F6" t="str">
-        <v/>
-      </c>
-      <c r="G6" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>Javier</v>
-      </c>
-      <c r="B7" t="str">
-        <v>López</v>
-      </c>
-      <c r="C7" t="str">
-        <v>El sistema respondió correctamente durante toda la prueba.</v>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D5" t="s">
+        <v>22</v>
+      </c>
+      <c r="E5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>23</v>
+      </c>
+      <c r="B6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" t="s">
+        <v>25</v>
+      </c>
+      <c r="D6" t="s">
+        <v>26</v>
+      </c>
+      <c r="E6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F6" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>27</v>
+      </c>
+      <c r="B7" t="s">
+        <v>28</v>
+      </c>
+      <c r="C7" t="s">
+        <v>29</v>
       </c>
       <c r="D7">
         <v>5</v>
       </c>
-      <c r="E7" t="str">
-        <v/>
-      </c>
-      <c r="F7" t="str">
-        <v/>
-      </c>
-      <c r="G7" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>Sonia</v>
-      </c>
-      <c r="B8" t="str">
-        <v>Navarro</v>
-      </c>
-      <c r="C8" t="str">
-        <v>Necesitamos más filtros para encontrar la información.</v>
+      <c r="E7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>30</v>
+      </c>
+      <c r="B8" t="s">
+        <v>31</v>
+      </c>
+      <c r="C8" t="s">
+        <v>32</v>
       </c>
       <c r="D8">
         <v>3</v>
       </c>
-      <c r="E8" t="str">
-        <v/>
-      </c>
-      <c r="F8" t="str">
-        <v/>
-      </c>
-      <c r="G8" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>Álex</v>
-      </c>
-      <c r="B9" t="str">
-        <v>Romero</v>
-      </c>
-      <c r="C9" t="str">
-        <v>El cálculo mostrado no coincide con el esperado.</v>
+      <c r="E8" t="s">
+        <v>10</v>
+      </c>
+      <c r="F8" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>33</v>
+      </c>
+      <c r="B9" t="s">
+        <v>34</v>
+      </c>
+      <c r="C9" t="s">
+        <v>35</v>
       </c>
       <c r="D9">
         <v>2</v>
       </c>
-      <c r="E9" t="str">
-        <v/>
-      </c>
-      <c r="F9" t="str">
-        <v/>
-      </c>
-      <c r="G9" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>Ana prueba</v>
-      </c>
-      <c r="B10" t="str">
-        <v/>
-      </c>
-      <c r="C10" t="str">
-        <v>El pedido llegó tarde, con el envase roto y nadie avisó</v>
-      </c>
-      <c r="D10" t="str">
-        <v/>
-      </c>
-      <c r="E10" t="str">
-        <v>2026-10-23T15:45:52.000Z</v>
-      </c>
-      <c r="F10">
+      <c r="E9" t="s">
+        <v>10</v>
+      </c>
+      <c r="F9" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>36</v>
+      </c>
+      <c r="B10" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10" t="s">
+        <v>37</v>
+      </c>
+      <c r="D10">
         <v>1</v>
       </c>
-      <c r="G10" t="str">
-        <v>1a16970c12b383d6</v>
+      <c r="E10" t="s">
+        <v>38</v>
+      </c>
+      <c r="F10" t="s">
+        <v>39</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G10"/>
+    <ignoredError sqref="A2:E9 A1:C1 F1 E1 A10:C10 F10 E10 F2:F9" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/reviews-clients.xlsx
+++ b/data/reviews-clients.xlsx
@@ -192,6 +192,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>

--- a/data/reviews-clients.xlsx
+++ b/data/reviews-clients.xlsx
@@ -1,152 +1,41 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://eurecatcloud-my.sharepoint.com/personal/alana_olivieri_eurecat_org/Documents/Formaciones/DonaIndustria4.0/Dia_3/Recursos/n8n-automation/data/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="11_4E17431850397D6A206102AB8855B237A12CC87D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{637644BD-1393-43F0-8829-7C5EEAA365CA}"/>
-  <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
-  </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="40">
-  <si>
-    <t>Nombre</t>
-  </si>
-  <si>
-    <t>Apellido</t>
-  </si>
-  <si>
-    <t>Review</t>
-  </si>
-  <si>
-    <t>Fecha</t>
-  </si>
-  <si>
-    <t>Valoración</t>
-  </si>
-  <si>
-    <t>Email_ID</t>
-  </si>
-  <si>
-    <t>Laura</t>
-  </si>
-  <si>
-    <t>Martínez</t>
-  </si>
-  <si>
-    <t>La máquina se detuvo dos veces durante el turno.</t>
-  </si>
-  <si>
-    <t>2.0</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>Carlos</t>
-  </si>
-  <si>
-    <t>Ruiz</t>
-  </si>
-  <si>
-    <t>El proceso fue estable y sin incidencias.</t>
-  </si>
-  <si>
-    <t>5.5</t>
-  </si>
-  <si>
-    <t>Marta</t>
-  </si>
-  <si>
-    <t>Gómez</t>
-  </si>
-  <si>
-    <t>La interfaz es clara, pero el informe tarda en cargar.</t>
-  </si>
-  <si>
-    <t>3.6</t>
-  </si>
-  <si>
-    <t>Diego</t>
-  </si>
-  <si>
-    <t>Santos</t>
-  </si>
-  <si>
-    <t>Se perdieron datos al importar el archivo.</t>
-  </si>
-  <si>
-    <t>1.7</t>
-  </si>
-  <si>
-    <t>Nuria</t>
-  </si>
-  <si>
-    <t>Pérez</t>
-  </si>
-  <si>
-    <t>Buen funcionamiento general.</t>
-  </si>
-  <si>
-    <t>4.5</t>
-  </si>
-  <si>
-    <t>Javier</t>
-  </si>
-  <si>
-    <t>López</t>
-  </si>
-  <si>
-    <t>El sistema respondió correctamente durante toda la prueba.</t>
-  </si>
-  <si>
-    <t>Sonia</t>
-  </si>
-  <si>
-    <t>Navarro</t>
-  </si>
-  <si>
-    <t>Necesitamos más filtros para encontrar la información.</t>
-  </si>
-  <si>
-    <t>Álex</t>
-  </si>
-  <si>
-    <t>Romero</t>
-  </si>
-  <si>
-    <t>El cálculo mostrado no coincide con el esperado.</t>
-  </si>
-  <si>
-    <t>Ana prueba</t>
-  </si>
-  <si>
-    <t>El pedido llegó tarde, con el envase roto y nadie avisó</t>
-  </si>
-  <si>
-    <t>2026-10-23T15:45:52.000Z</t>
-  </si>
-  <si>
-    <t>1a16970c12b383d6</t>
-  </si>
-</sst>
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
+  <numFmts count="1">
+    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
+  </numFmts>
+  <fonts count="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -176,26 +65,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -519,214 +396,232 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F10"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F11"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B4" t="s">
-        <v>16</v>
-      </c>
-      <c r="C4" t="s">
-        <v>17</v>
-      </c>
-      <c r="D4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>19</v>
-      </c>
-      <c r="B5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C5" t="s">
-        <v>21</v>
-      </c>
-      <c r="D5" t="s">
-        <v>22</v>
-      </c>
-      <c r="E5" t="s">
-        <v>10</v>
-      </c>
-      <c r="F5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>23</v>
-      </c>
-      <c r="B6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C6" t="s">
-        <v>25</v>
-      </c>
-      <c r="D6" t="s">
-        <v>26</v>
-      </c>
-      <c r="E6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F6" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>27</v>
-      </c>
-      <c r="B7" t="s">
-        <v>28</v>
-      </c>
-      <c r="C7" t="s">
-        <v>29</v>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Nombre</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Apellido</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Review</v>
+      </c>
+      <c r="D1" t="str">
+        <v>Valoración</v>
+      </c>
+      <c r="E1" t="str">
+        <v>Fecha</v>
+      </c>
+      <c r="F1" t="str">
+        <v>Email_ID</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>Laura</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Martínez</v>
+      </c>
+      <c r="C2" t="str">
+        <v>La máquina se detuvo dos veces durante el turno.</v>
+      </c>
+      <c r="D2" t="str">
+        <v>2.0</v>
+      </c>
+      <c r="E2" t="str">
+        <v/>
+      </c>
+      <c r="F2" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>Carlos</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Ruiz</v>
+      </c>
+      <c r="C3" t="str">
+        <v>El proceso fue estable y sin incidencias.</v>
+      </c>
+      <c r="D3" t="str">
+        <v>5.5</v>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>Marta</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Gómez</v>
+      </c>
+      <c r="C4" t="str">
+        <v>La interfaz es clara, pero el informe tarda en cargar.</v>
+      </c>
+      <c r="D4" t="str">
+        <v>3.6</v>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>Diego</v>
+      </c>
+      <c r="B5" t="str">
+        <v>Santos</v>
+      </c>
+      <c r="C5" t="str">
+        <v>Se perdieron datos al importar el archivo.</v>
+      </c>
+      <c r="D5" t="str">
+        <v>1.7</v>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>Nuria</v>
+      </c>
+      <c r="B6" t="str">
+        <v>Pérez</v>
+      </c>
+      <c r="C6" t="str">
+        <v>Buen funcionamiento general.</v>
+      </c>
+      <c r="D6" t="str">
+        <v>4.5</v>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>Javier</v>
+      </c>
+      <c r="B7" t="str">
+        <v>López</v>
+      </c>
+      <c r="C7" t="str">
+        <v>El sistema respondió correctamente durante toda la prueba.</v>
       </c>
       <c r="D7">
         <v>5</v>
       </c>
-      <c r="E7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F7" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
-        <v>30</v>
-      </c>
-      <c r="B8" t="s">
-        <v>31</v>
-      </c>
-      <c r="C8" t="s">
-        <v>32</v>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>Sonia</v>
+      </c>
+      <c r="B8" t="str">
+        <v>Navarro</v>
+      </c>
+      <c r="C8" t="str">
+        <v>Necesitamos más filtros para encontrar la información.</v>
       </c>
       <c r="D8">
         <v>3</v>
       </c>
-      <c r="E8" t="s">
-        <v>10</v>
-      </c>
-      <c r="F8" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
-        <v>33</v>
-      </c>
-      <c r="B9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C9" t="s">
-        <v>35</v>
+      <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>Álex</v>
+      </c>
+      <c r="B9" t="str">
+        <v>Romero</v>
+      </c>
+      <c r="C9" t="str">
+        <v>El cálculo mostrado no coincide con el esperado.</v>
       </c>
       <c r="D9">
         <v>2</v>
       </c>
-      <c r="E9" t="s">
-        <v>10</v>
-      </c>
-      <c r="F9" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
-        <v>36</v>
-      </c>
-      <c r="B10" t="s">
-        <v>10</v>
-      </c>
-      <c r="C10" t="s">
-        <v>37</v>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>Ana prueba</v>
+      </c>
+      <c r="B10" t="str">
+        <v/>
+      </c>
+      <c r="C10" t="str">
+        <v>El pedido llegó tarde, con el envase roto y nadie avisó</v>
       </c>
       <c r="D10">
         <v>1</v>
       </c>
-      <c r="E10" t="s">
-        <v>38</v>
-      </c>
-      <c r="F10" t="s">
-        <v>39</v>
+      <c r="E10" t="str">
+        <v>2026-10-23T15:45:52.000Z</v>
+      </c>
+      <c r="F10" t="str">
+        <v>1a16970c12b383d6</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>prueba juan</v>
+      </c>
+      <c r="B11" t="str">
+        <v/>
+      </c>
+      <c r="C11" t="str">
+        <v>El pedido y todo perfecto</v>
+      </c>
+      <c r="D11">
+        <v>5</v>
+      </c>
+      <c r="E11" t="str">
+        <v>2026-10-23T15:56:19.000Z</v>
+      </c>
+      <c r="F11" t="str">
+        <v>1a1697a45682b1eb</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A2:E9 A1:C1 F1 E1 A10:C10 F10 E10 F2:F9" numberStoredAsText="1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F11"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/reviews-clients.xlsx
+++ b/data/reviews-clients.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F12"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -619,9 +619,29 @@
         <v>1a1697a45682b1eb</v>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>test alexa</v>
+      </c>
+      <c r="B12" t="str">
+        <v/>
+      </c>
+      <c r="C12" t="str">
+        <v>El pedido llegó incompleto</v>
+      </c>
+      <c r="D12">
+        <v>1</v>
+      </c>
+      <c r="E12" t="str">
+        <v>2026-10-23T16:01:15.000Z</v>
+      </c>
+      <c r="F12" t="str">
+        <v>1a1697ec896664d8</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F12"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/reviews-clients.xlsx
+++ b/data/reviews-clients.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F13"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -639,9 +639,29 @@
         <v>1a1697ec896664d8</v>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>María García</v>
+      </c>
+      <c r="B13" t="str">
+        <v/>
+      </c>
+      <c r="C13" t="str">
+        <v>El pedido llegó tarde y el producto estaba dañado.</v>
+      </c>
+      <c r="D13">
+        <v>1</v>
+      </c>
+      <c r="E13" t="str">
+        <v>2026-10-26T18:42:03.647Z</v>
+      </c>
+      <c r="F13" t="str">
+        <v>PRUEBA-001</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F12"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F13"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/reviews-clients.xlsx
+++ b/data/reviews-clients.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F14"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -659,9 +659,29 @@
         <v>PRUEBA-001</v>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>Ana pruebazdskj</v>
+      </c>
+      <c r="B14" t="str">
+        <v/>
+      </c>
+      <c r="C14" t="str">
+        <v>El pedido llegó tarde, con el envase roto y nadie avisó</v>
+      </c>
+      <c r="D14">
+        <v>1</v>
+      </c>
+      <c r="E14" t="str">
+        <v>2026-10-26T18:54:34.000Z</v>
+      </c>
+      <c r="F14" t="str">
+        <v>1a179908643f6518</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F13"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F14"/>
   </ignoredErrors>
 </worksheet>
 </file>